--- a/PATXOT 512/Mayo/PATXOT 521 MAYO.xlsx
+++ b/PATXOT 512/Mayo/PATXOT 521 MAYO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865DE2B2-DF77-448D-ACFC-D8C6B82E0DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2646D9A-7115-4A52-BFCA-3FD3B96717A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -425,12 +425,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="d/m"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="d/m"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1398,11 +1398,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1413,7 +1413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1436,14 +1436,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1460,7 +1460,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1468,10 +1468,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1480,7 +1480,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1493,7 +1493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1506,7 +1506,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1533,8 +1533,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1542,8 +1542,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1554,11 +1554,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1569,7 +1569,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1603,12 +1603,12 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1638,16 +1638,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1657,7 +1657,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1668,20 +1668,53 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1695,47 +1728,10 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1749,8 +1745,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2122,16 +2121,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2139,93 +2138,93 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="170" t="s">
         <v>128</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="87" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="76"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="172">
+      <c r="C17" s="203">
         <v>74186.03</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="76"/>
       <c r="B18" s="88"/>
       <c r="C18" s="85"/>
       <c r="D18" s="48"/>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="76"/>
       <c r="B19" s="88"/>
       <c r="C19" s="85"/>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="89"/>
       <c r="B20" s="90"/>
       <c r="C20" s="61">
@@ -2233,14 +2232,14 @@
         <v>74186.03</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="87" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="88"/>
       <c r="C21" s="91"/>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="76" t="s">
         <v>129</v>
       </c>
@@ -2250,29 +2249,29 @@
       </c>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="76" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="92"/>
-      <c r="C23" s="171">
+      <c r="C23" s="85">
         <v>36534.6</v>
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="76"/>
       <c r="B24" s="92"/>
       <c r="C24" s="85"/>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="76"/>
       <c r="B25" s="92"/>
       <c r="C25" s="85"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="76" t="s">
         <v>127</v>
       </c>
@@ -2284,7 +2283,7 @@
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="89"/>
       <c r="B27" s="90"/>
       <c r="C27" s="61">
@@ -2293,7 +2292,7 @@
       </c>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="80" t="s">
         <v>79</v>
       </c>
@@ -2304,40 +2303,40 @@
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C29" s="62"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="62"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="76"/>
       <c r="B31" s="76"/>
       <c r="C31" s="85"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="76"/>
       <c r="B32" s="76"/>
       <c r="C32" s="86"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="76"/>
       <c r="B33" s="76"/>
       <c r="C33" s="86"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="64"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
         <v>41</v>
       </c>
@@ -2348,7 +2347,7 @@
       </c>
       <c r="E35" s="14"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>15</v>
       </c>
@@ -2358,48 +2357,48 @@
         <v>290720.63</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="147" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="148"/>
       <c r="C39" s="149"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="145" t="s">
         <v>10</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="146">
-        <v>-225247.17452636751</v>
+        <v>3596.7637403397239</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="32">
         <f>'prorrateo '!F15</f>
-        <v>234321.66826670722</v>
+        <v>155477.73000000001</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>80</v>
       </c>
       <c r="C42" s="94">
         <f>-edesur!H1</f>
-        <v>0</v>
+        <v>-10296.959999999999</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -2408,34 +2407,34 @@
         <v>-140720.63</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="33"/>
       <c r="C44" s="40">
         <f>SUM(C40:C43)</f>
-        <v>-131646.1362596603</v>
+        <v>8056.9037403397379</v>
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
       <c r="B45" s="18"/>
       <c r="C45" s="20"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
       <c r="F46" s="95"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
     </row>
-    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="74" t="s">
         <v>58</v>
       </c>
@@ -2444,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="76" t="s">
         <v>64</v>
       </c>
@@ -2454,17 +2453,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="76"/>
       <c r="B50" s="76"/>
       <c r="C50" s="83"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="76"/>
       <c r="B51" s="76"/>
       <c r="C51" s="84"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="80" t="s">
         <v>4</v>
       </c>
@@ -2474,22 +2473,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -2511,32 +2510,32 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="53" t="s">
         <v>49</v>
       </c>
       <c r="E1" s="50">
-        <v>291359.89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>290720.63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="98">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2553,15 +2552,15 @@
       <c r="K2" s="102"/>
       <c r="L2" s="103"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="196" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="186" t="s">
+      <c r="B3" s="180"/>
+      <c r="C3" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="194" t="s">
+      <c r="D3" s="177" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2570,62 +2569,62 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="175" t="s">
         <v>54</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="192" t="s">
+      <c r="I3" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="188" t="s">
+      <c r="J3" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="186" t="s">
+      <c r="K3" s="175" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="198"/>
-      <c r="B4" s="199"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="195"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="181"/>
+      <c r="B4" s="182"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="187"/>
+      <c r="G4" s="176"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="193"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="187"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="176"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="190">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="171">
         <v>1</v>
       </c>
-      <c r="B5" s="191"/>
+      <c r="B5" s="172"/>
       <c r="C5" s="111" t="s">
         <v>66</v>
       </c>
       <c r="D5" s="59"/>
       <c r="E5" s="150">
-        <v>31310.712786555188</v>
+        <v>21455.926740000003</v>
       </c>
       <c r="F5" s="151">
         <f t="shared" ref="F5:F9" si="0">E5</f>
-        <v>31310.712786555188</v>
+        <v>21455.926740000003</v>
       </c>
       <c r="G5" s="152">
         <f>E5-F5</f>
@@ -2640,22 +2639,22 @@
       </c>
       <c r="J5" s="97">
         <f>E$1*I5/100</f>
-        <v>40207.664820000005</v>
+        <v>40119.446940000002</v>
       </c>
       <c r="K5" s="143">
         <f>edesur!H5</f>
-        <v>0</v>
+        <v>1411.9577257525084</v>
       </c>
       <c r="L5" s="104">
         <f>G5+H5+J5+K5</f>
-        <v>40207.664820000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="190">
+        <v>41531.40466575251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="171">
         <v>2</v>
       </c>
-      <c r="B6" s="191"/>
+      <c r="B6" s="172"/>
       <c r="C6" s="111" t="s">
         <v>67</v>
       </c>
@@ -2663,11 +2662,11 @@
         <v>72</v>
       </c>
       <c r="E6" s="150">
-        <v>30871.318343297658</v>
+        <v>18439.658778000001</v>
       </c>
       <c r="F6" s="151">
         <f t="shared" si="0"/>
-        <v>30871.318343297658</v>
+        <v>18439.658778000001</v>
       </c>
       <c r="G6" s="152">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
@@ -2682,22 +2681,22 @@
       </c>
       <c r="J6" s="97">
         <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>34555.282954000002</v>
+        <v>34479.466717999996</v>
       </c>
       <c r="K6" s="143">
         <f>edesur!H6</f>
-        <v>0</v>
+        <v>1687.4616722408025</v>
       </c>
       <c r="L6" s="104">
         <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>34555.282954000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="190">
+        <v>36166.928390240799</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="171">
         <v>3</v>
       </c>
-      <c r="B7" s="191"/>
+      <c r="B7" s="172"/>
       <c r="C7" s="111" t="s">
         <v>67</v>
       </c>
@@ -2705,11 +2704,11 @@
         <v>73</v>
       </c>
       <c r="E7" s="150">
-        <v>31575.545756876258</v>
+        <v>19372.525158</v>
       </c>
       <c r="F7" s="151">
         <f t="shared" si="0"/>
-        <v>31575.545756876258</v>
+        <v>19372.525158</v>
       </c>
       <c r="G7" s="152">
         <f t="shared" si="1"/>
@@ -2724,22 +2723,22 @@
       </c>
       <c r="J7" s="97">
         <f t="shared" si="3"/>
-        <v>36303.442294000008</v>
+        <v>36223.790498000002</v>
       </c>
       <c r="K7" s="143">
         <f>edesur!H7</f>
-        <v>0</v>
+        <v>1670.2426755852841</v>
       </c>
       <c r="L7" s="104">
         <f t="shared" si="4"/>
-        <v>36303.442294000008</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="190">
+        <v>37894.033173585289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="171">
         <v>4</v>
       </c>
-      <c r="B8" s="191"/>
+      <c r="B8" s="172"/>
       <c r="C8" s="111" t="s">
         <v>68</v>
       </c>
@@ -2747,11 +2746,11 @@
         <v>74</v>
       </c>
       <c r="E8" s="150">
-        <v>36252.089402090307</v>
+        <v>22932.965175000001</v>
       </c>
       <c r="F8" s="151">
         <f t="shared" si="0"/>
-        <v>36252.089402090307</v>
+        <v>22932.965175000001</v>
       </c>
       <c r="G8" s="152">
         <f t="shared" si="1"/>
@@ -2766,22 +2765,22 @@
       </c>
       <c r="J8" s="97">
         <f t="shared" si="3"/>
-        <v>42975.583775000006</v>
+        <v>42881.292925000002</v>
       </c>
       <c r="K8" s="143">
         <f>edesur!H8</f>
-        <v>0</v>
+        <v>1842.432642140468</v>
       </c>
       <c r="L8" s="104">
         <f t="shared" si="4"/>
-        <v>42975.583775000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="190">
+        <v>44723.725567140471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="171">
         <v>5</v>
       </c>
-      <c r="B9" s="191"/>
+      <c r="B9" s="172"/>
       <c r="C9" s="111" t="s">
         <v>69</v>
       </c>
@@ -2789,11 +2788,11 @@
         <v>75</v>
       </c>
       <c r="E9" s="150">
-        <v>26179.162034284283</v>
+        <v>19294.786293000001</v>
       </c>
       <c r="F9" s="151">
         <f t="shared" si="0"/>
-        <v>26179.162034284283</v>
+        <v>19294.786293000001</v>
       </c>
       <c r="G9" s="152">
         <f t="shared" si="1"/>
@@ -2808,32 +2807,32 @@
       </c>
       <c r="J9" s="97">
         <f t="shared" si="3"/>
-        <v>36157.762348999997</v>
+        <v>36078.430183000004</v>
       </c>
       <c r="K9" s="143">
         <f>edesur!H9</f>
-        <v>0</v>
+        <v>1033.1397993311036</v>
       </c>
       <c r="L9" s="104">
         <f>G9+H9+J9+K9</f>
-        <v>36157.762348999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="190">
+        <v>37111.569982331108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="171">
         <v>6</v>
       </c>
-      <c r="B10" s="191"/>
+      <c r="B10" s="172"/>
       <c r="C10" s="111" t="s">
         <v>70</v>
       </c>
       <c r="D10" s="73"/>
       <c r="E10" s="150">
-        <v>26422.052583705688</v>
+        <v>19403.620704000001</v>
       </c>
       <c r="F10" s="151">
         <f>E10</f>
-        <v>26422.052583705688</v>
+        <v>19403.620704000001</v>
       </c>
       <c r="G10" s="152">
         <f t="shared" si="1"/>
@@ -2848,32 +2847,32 @@
       </c>
       <c r="J10" s="97">
         <f t="shared" si="3"/>
-        <v>36361.714272000005</v>
+        <v>36281.934624000001</v>
       </c>
       <c r="K10" s="143">
         <f>edesur!H10</f>
-        <v>0</v>
+        <v>1050.358795986622</v>
       </c>
       <c r="L10" s="104">
         <f t="shared" si="4"/>
-        <v>36361.714272000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="190">
+        <v>37332.293419986621</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="171">
         <v>7</v>
       </c>
-      <c r="B11" s="191"/>
+      <c r="B11" s="172"/>
       <c r="C11" s="111" t="s">
         <v>71</v>
       </c>
       <c r="D11" s="73"/>
       <c r="E11" s="150">
-        <v>39198.725671190645</v>
+        <v>28390.233498000005</v>
       </c>
       <c r="F11" s="151">
         <f>E11</f>
-        <v>39198.725671190645</v>
+        <v>28390.233498000005</v>
       </c>
       <c r="G11" s="152">
         <f t="shared" si="1"/>
@@ -2888,33 +2887,33 @@
       </c>
       <c r="J11" s="97">
         <f t="shared" si="3"/>
-        <v>53202.315914000006</v>
+        <v>53085.587038000005</v>
       </c>
       <c r="K11" s="143">
         <f>edesur!H11</f>
-        <v>0</v>
+        <v>1601.3666889632107</v>
       </c>
       <c r="L11" s="104">
         <f t="shared" si="4"/>
-        <v>53202.315914000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="190" t="s">
+        <v>54686.953726963213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="171" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="191"/>
+      <c r="B12" s="172"/>
       <c r="C12" s="111" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="73"/>
       <c r="E12" s="150">
-        <v>4212.6036841376008</v>
+        <v>2083.4015820000004</v>
       </c>
       <c r="F12" s="151">
         <f t="shared" ref="F12:F14" si="5">E12</f>
-        <v>4212.6036841376008</v>
+        <v>2083.4015820000004</v>
       </c>
       <c r="G12" s="152">
         <f t="shared" si="1"/>
@@ -2929,32 +2928,32 @@
       </c>
       <c r="J12" s="97">
         <f t="shared" si="3"/>
-        <v>3904.2225260000005</v>
+        <v>3895.6564420000004</v>
       </c>
       <c r="K12" s="143">
         <v>0</v>
       </c>
       <c r="L12" s="104">
         <f t="shared" si="4"/>
-        <v>3904.2225260000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="190" t="s">
+        <v>3895.6564420000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="171" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="191"/>
+      <c r="B13" s="172"/>
       <c r="C13" s="111" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="73"/>
       <c r="E13" s="150">
-        <v>4149.7290022848001</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="F13" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="G13" s="152">
         <f t="shared" si="1"/>
@@ -2969,32 +2968,32 @@
       </c>
       <c r="J13" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>3837.5123159999998</v>
       </c>
       <c r="K13" s="143">
         <v>0</v>
       </c>
       <c r="L13" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="190" t="s">
+        <v>3837.5123159999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="191"/>
+      <c r="B14" s="172"/>
       <c r="C14" s="59" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="73"/>
       <c r="E14" s="150">
-        <v>4149.7290022848001</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="F14" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="G14" s="152">
         <f t="shared" si="1"/>
@@ -3009,17 +3008,17 @@
       </c>
       <c r="J14" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>3837.5123159999998</v>
       </c>
       <c r="K14" s="143">
         <v>0</v>
       </c>
       <c r="L14" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3837.5123159999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="105" t="s">
         <v>11</v>
       </c>
@@ -3028,11 +3027,11 @@
       <c r="D15" s="107"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>234321.66826670722</v>
+        <v>155477.73000000001</v>
       </c>
       <c r="F15" s="108">
         <f>SUM(F5:F14)</f>
-        <v>234321.66826670722</v>
+        <v>155477.73000000001</v>
       </c>
       <c r="G15" s="108"/>
       <c r="H15" s="109">
@@ -3045,18 +3044,18 @@
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>291359.89</v>
+        <v>290720.63</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>0</v>
+        <v>10296.959999999999</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>291359.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>301017.59000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>50</v>
       </c>
@@ -3064,7 +3063,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>52</v>
       </c>
@@ -3082,7 +3081,7 @@
       <c r="K19" s="54"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3114,7 +3113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3140,7 +3139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3243,7 +3242,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3274,7 +3273,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3336,7 +3335,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3370,7 +3369,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3404,7 +3403,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3437,44 +3436,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="177" t="s">
+      <c r="E32" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="178"/>
-      <c r="G32" s="178"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="178"/>
-      <c r="J32" s="178"/>
-      <c r="K32" s="176"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="186"/>
+      <c r="H32" s="186"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="186"/>
+      <c r="K32" s="187"/>
       <c r="L32" s="153"/>
       <c r="M32" s="154"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="179" t="s">
+      <c r="E33" s="188" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="178"/>
-      <c r="G33" s="178"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="178"/>
-      <c r="J33" s="178"/>
-      <c r="K33" s="176"/>
+      <c r="F33" s="186"/>
+      <c r="G33" s="186"/>
+      <c r="H33" s="186"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="186"/>
+      <c r="K33" s="187"/>
       <c r="L33" s="155"/>
       <c r="M33" s="156"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="153"/>
@@ -3491,7 +3490,7 @@
       <c r="M34" s="156"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="155" t="s">
@@ -3507,7 +3506,7 @@
       <c r="M35" s="156"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="159"/>
@@ -3521,23 +3520,23 @@
       <c r="M36" s="156"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="180" t="s">
+      <c r="E37" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="181"/>
-      <c r="G37" s="181"/>
-      <c r="H37" s="181"/>
-      <c r="I37" s="181"/>
-      <c r="J37" s="181"/>
-      <c r="K37" s="182"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="190"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="190"/>
+      <c r="J37" s="190"/>
+      <c r="K37" s="191"/>
       <c r="L37" s="155"/>
       <c r="M37" s="156"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="155"/>
@@ -3551,7 +3550,7 @@
       <c r="M38" s="156"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="155" t="s">
@@ -3570,13 +3569,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="156"/>
-      <c r="L39" s="183" t="s">
+      <c r="L39" s="192" t="s">
         <v>118</v>
       </c>
-      <c r="M39" s="184"/>
+      <c r="M39" s="193"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="155" t="s">
@@ -3594,7 +3593,7 @@
       <c r="M40" s="156"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="155"/>
@@ -3604,11 +3603,11 @@
       <c r="I41" s="158"/>
       <c r="J41" s="158"/>
       <c r="K41" s="156"/>
-      <c r="L41" s="185"/>
-      <c r="M41" s="184"/>
+      <c r="L41" s="194"/>
+      <c r="M41" s="193"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="155" t="s">
@@ -3620,14 +3619,14 @@
       <c r="I42" s="158"/>
       <c r="J42" s="164">
         <f>J7</f>
-        <v>36303.442294000008</v>
+        <v>36223.790498000002</v>
       </c>
       <c r="K42" s="156"/>
       <c r="L42" s="155"/>
       <c r="M42" s="156"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="165" t="s">
@@ -3639,14 +3638,14 @@
       <c r="I43" s="158"/>
       <c r="J43" s="164">
         <f>K7</f>
-        <v>0</v>
+        <v>1670.2426755852841</v>
       </c>
       <c r="K43" s="156"/>
       <c r="L43" s="155"/>
       <c r="M43" s="156"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="165" t="s">
@@ -3665,7 +3664,7 @@
       <c r="M44" s="156"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="165"/>
@@ -3679,7 +3678,7 @@
       <c r="M45" s="156"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="165"/>
@@ -3693,7 +3692,7 @@
       <c r="M46" s="156"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="158"/>
@@ -3706,7 +3705,7 @@
       <c r="M47" s="156"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="165"/>
@@ -3720,7 +3719,7 @@
       <c r="M48" s="156"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="155"/>
@@ -3734,7 +3733,7 @@
       <c r="M49" s="156"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="155" t="s">
@@ -3753,7 +3752,7 @@
       <c r="M50" s="156"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="155"/>
@@ -3767,58 +3766,58 @@
       <c r="M51" s="167"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="173" t="s">
+      <c r="E52" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="174"/>
-      <c r="G52" s="174"/>
-      <c r="H52" s="174"/>
-      <c r="I52" s="174"/>
-      <c r="J52" s="175">
+      <c r="F52" s="196"/>
+      <c r="G52" s="196"/>
+      <c r="H52" s="196"/>
+      <c r="I52" s="196"/>
+      <c r="J52" s="197">
         <f>SUM(J42:J51)</f>
-        <v>36379.242294000011</v>
-      </c>
-      <c r="K52" s="176"/>
+        <v>37969.833173585292</v>
+      </c>
+      <c r="K52" s="187"/>
       <c r="L52" s="168"/>
       <c r="M52" s="169"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="177" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="178"/>
-      <c r="G56" s="178"/>
-      <c r="H56" s="178"/>
-      <c r="I56" s="178"/>
-      <c r="J56" s="178"/>
-      <c r="K56" s="176"/>
+      <c r="F56" s="186"/>
+      <c r="G56" s="186"/>
+      <c r="H56" s="186"/>
+      <c r="I56" s="186"/>
+      <c r="J56" s="186"/>
+      <c r="K56" s="187"/>
       <c r="L56" s="153"/>
       <c r="M56" s="154"/>
     </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="179" t="s">
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="188" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="178"/>
-      <c r="G57" s="178"/>
-      <c r="H57" s="178"/>
-      <c r="I57" s="178"/>
-      <c r="J57" s="178"/>
-      <c r="K57" s="176"/>
+      <c r="F57" s="186"/>
+      <c r="G57" s="186"/>
+      <c r="H57" s="186"/>
+      <c r="I57" s="186"/>
+      <c r="J57" s="186"/>
+      <c r="K57" s="187"/>
       <c r="L57" s="155"/>
       <c r="M57" s="156"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E58" s="153"/>
       <c r="F58" s="157"/>
       <c r="G58" s="157"/>
@@ -3832,7 +3831,7 @@
       <c r="L58" s="155"/>
       <c r="M58" s="156"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E59" s="155" t="s">
         <v>115</v>
       </c>
@@ -3845,7 +3844,7 @@
       <c r="L59" s="155"/>
       <c r="M59" s="156"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E60" s="159"/>
       <c r="F60" s="160"/>
       <c r="G60" s="160"/>
@@ -3856,20 +3855,20 @@
       <c r="L60" s="155"/>
       <c r="M60" s="156"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="180" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="F61" s="181"/>
-      <c r="G61" s="181"/>
-      <c r="H61" s="181"/>
-      <c r="I61" s="181"/>
-      <c r="J61" s="181"/>
-      <c r="K61" s="182"/>
+      <c r="F61" s="190"/>
+      <c r="G61" s="190"/>
+      <c r="H61" s="190"/>
+      <c r="I61" s="190"/>
+      <c r="J61" s="190"/>
+      <c r="K61" s="191"/>
       <c r="L61" s="155"/>
       <c r="M61" s="156"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E62" s="155"/>
       <c r="F62" s="158"/>
       <c r="G62" s="158"/>
@@ -3880,7 +3879,7 @@
       <c r="L62" s="155"/>
       <c r="M62" s="156"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E63" s="155" t="s">
         <v>116</v>
       </c>
@@ -3897,12 +3896,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="156"/>
-      <c r="L63" s="183" t="s">
+      <c r="L63" s="192" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="184"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="193"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="155" t="s">
         <v>119</v>
       </c>
@@ -3917,7 +3916,7 @@
       <c r="L64" s="155"/>
       <c r="M64" s="156"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E65" s="155"/>
       <c r="F65" s="158"/>
       <c r="G65" s="158"/>
@@ -3925,10 +3924,10 @@
       <c r="I65" s="158"/>
       <c r="J65" s="158"/>
       <c r="K65" s="156"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="184"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="194"/>
+      <c r="M65" s="193"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="155" t="s">
         <v>49</v>
       </c>
@@ -3938,13 +3937,13 @@
       <c r="I66" s="158"/>
       <c r="J66" s="164">
         <f>J8</f>
-        <v>42975.583775000006</v>
+        <v>42881.292925000002</v>
       </c>
       <c r="K66" s="156"/>
       <c r="L66" s="155"/>
       <c r="M66" s="156"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E67" s="165" t="s">
         <v>120</v>
       </c>
@@ -3954,13 +3953,13 @@
       <c r="I67" s="158"/>
       <c r="J67" s="164">
         <f>K8</f>
-        <v>0</v>
+        <v>1842.432642140468</v>
       </c>
       <c r="K67" s="156"/>
       <c r="L67" s="155"/>
       <c r="M67" s="156"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E68" s="165" t="s">
         <v>122</v>
       </c>
@@ -3976,7 +3975,7 @@
       <c r="L68" s="155"/>
       <c r="M68" s="156"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E69" s="165"/>
       <c r="F69" s="158"/>
       <c r="G69" s="158"/>
@@ -3987,7 +3986,7 @@
       <c r="L69" s="155"/>
       <c r="M69" s="156"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E70" s="165"/>
       <c r="F70" s="158"/>
       <c r="G70" s="158"/>
@@ -3998,7 +3997,7 @@
       <c r="L70" s="155"/>
       <c r="M70" s="156"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="F71" s="158"/>
       <c r="G71" s="158"/>
       <c r="H71" s="158"/>
@@ -4008,7 +4007,7 @@
       <c r="L71" s="155"/>
       <c r="M71" s="156"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E72" s="165"/>
       <c r="F72" s="158"/>
       <c r="G72" s="158"/>
@@ -4019,7 +4018,7 @@
       <c r="L72" s="155"/>
       <c r="M72" s="156"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E73" s="155"/>
       <c r="F73" s="158"/>
       <c r="G73" s="158"/>
@@ -4030,7 +4029,7 @@
       <c r="L73" s="155"/>
       <c r="M73" s="156"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E74" s="155"/>
       <c r="F74" s="158"/>
       <c r="G74" s="158"/>
@@ -4041,7 +4040,7 @@
       <c r="L74" s="155"/>
       <c r="M74" s="156"/>
     </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="155"/>
       <c r="F75" s="158"/>
       <c r="G75" s="158"/>
@@ -4052,50 +4051,50 @@
       <c r="L75" s="166"/>
       <c r="M75" s="167"/>
     </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="173" t="s">
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="F76" s="174"/>
-      <c r="G76" s="174"/>
-      <c r="H76" s="174"/>
-      <c r="I76" s="174"/>
-      <c r="J76" s="175">
+      <c r="F76" s="196"/>
+      <c r="G76" s="196"/>
+      <c r="H76" s="196"/>
+      <c r="I76" s="196"/>
+      <c r="J76" s="197">
         <f>SUM(J66:J75)</f>
-        <v>42975.583775000006</v>
-      </c>
-      <c r="K76" s="176"/>
+        <v>44723.725567140471</v>
+      </c>
+      <c r="K76" s="187"/>
       <c r="L76" s="168"/>
       <c r="M76" s="169"/>
     </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="177" t="s">
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="F83" s="178"/>
-      <c r="G83" s="178"/>
-      <c r="H83" s="178"/>
-      <c r="I83" s="178"/>
-      <c r="J83" s="178"/>
-      <c r="K83" s="176"/>
+      <c r="F83" s="186"/>
+      <c r="G83" s="186"/>
+      <c r="H83" s="186"/>
+      <c r="I83" s="186"/>
+      <c r="J83" s="186"/>
+      <c r="K83" s="187"/>
       <c r="L83" s="153"/>
       <c r="M83" s="154"/>
     </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="179" t="s">
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="188" t="s">
         <v>114</v>
       </c>
-      <c r="F84" s="178"/>
-      <c r="G84" s="178"/>
-      <c r="H84" s="178"/>
-      <c r="I84" s="178"/>
-      <c r="J84" s="178"/>
-      <c r="K84" s="176"/>
+      <c r="F84" s="186"/>
+      <c r="G84" s="186"/>
+      <c r="H84" s="186"/>
+      <c r="I84" s="186"/>
+      <c r="J84" s="186"/>
+      <c r="K84" s="187"/>
       <c r="L84" s="155"/>
       <c r="M84" s="156"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E85" s="153"/>
       <c r="F85" s="157"/>
       <c r="G85" s="157"/>
@@ -4109,7 +4108,7 @@
       <c r="L85" s="155"/>
       <c r="M85" s="156"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E86" s="155" t="s">
         <v>115</v>
       </c>
@@ -4122,7 +4121,7 @@
       <c r="L86" s="155"/>
       <c r="M86" s="156"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E87" s="159"/>
       <c r="F87" s="160"/>
       <c r="G87" s="160"/>
@@ -4133,20 +4132,20 @@
       <c r="L87" s="155"/>
       <c r="M87" s="156"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="180" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="F88" s="181"/>
-      <c r="G88" s="181"/>
-      <c r="H88" s="181"/>
-      <c r="I88" s="181"/>
-      <c r="J88" s="181"/>
-      <c r="K88" s="182"/>
+      <c r="F88" s="190"/>
+      <c r="G88" s="190"/>
+      <c r="H88" s="190"/>
+      <c r="I88" s="190"/>
+      <c r="J88" s="190"/>
+      <c r="K88" s="191"/>
       <c r="L88" s="155"/>
       <c r="M88" s="156"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E89" s="155"/>
       <c r="F89" s="158"/>
       <c r="G89" s="158"/>
@@ -4157,7 +4156,7 @@
       <c r="L89" s="155"/>
       <c r="M89" s="156"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E90" s="155" t="s">
         <v>116</v>
       </c>
@@ -4174,12 +4173,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="156"/>
-      <c r="L90" s="183" t="s">
+      <c r="L90" s="192" t="s">
         <v>118</v>
       </c>
-      <c r="M90" s="184"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M90" s="193"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="155" t="s">
         <v>119</v>
       </c>
@@ -4194,7 +4193,7 @@
       <c r="L91" s="155"/>
       <c r="M91" s="156"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E92" s="155"/>
       <c r="F92" s="158"/>
       <c r="G92" s="158"/>
@@ -4202,10 +4201,10 @@
       <c r="I92" s="158"/>
       <c r="J92" s="158"/>
       <c r="K92" s="156"/>
-      <c r="L92" s="185"/>
-      <c r="M92" s="184"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="194"/>
+      <c r="M92" s="193"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="155" t="s">
         <v>49</v>
       </c>
@@ -4215,13 +4214,13 @@
       <c r="I93" s="158"/>
       <c r="J93" s="164">
         <f>J10</f>
-        <v>36361.714272000005</v>
+        <v>36281.934624000001</v>
       </c>
       <c r="K93" s="156"/>
       <c r="L93" s="155"/>
       <c r="M93" s="156"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E94" s="165" t="s">
         <v>120</v>
       </c>
@@ -4231,13 +4230,13 @@
       <c r="I94" s="158"/>
       <c r="J94" s="164">
         <f>K10</f>
-        <v>0</v>
+        <v>1050.358795986622</v>
       </c>
       <c r="K94" s="156"/>
       <c r="L94" s="155"/>
       <c r="M94" s="156"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E95" s="165" t="s">
         <v>123</v>
       </c>
@@ -4252,7 +4251,7 @@
       <c r="L95" s="155"/>
       <c r="M95" s="156"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E96" s="165"/>
       <c r="F96" s="158"/>
       <c r="G96" s="158"/>
@@ -4263,7 +4262,7 @@
       <c r="L96" s="155"/>
       <c r="M96" s="156"/>
     </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="165"/>
       <c r="F97" s="158"/>
       <c r="G97" s="158"/>
@@ -4274,7 +4273,7 @@
       <c r="L97" s="155"/>
       <c r="M97" s="156"/>
     </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F98" s="158"/>
       <c r="G98" s="158"/>
       <c r="H98" s="158"/>
@@ -4284,7 +4283,7 @@
       <c r="L98" s="155"/>
       <c r="M98" s="156"/>
     </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="165"/>
       <c r="F99" s="158"/>
       <c r="G99" s="158"/>
@@ -4295,7 +4294,7 @@
       <c r="L99" s="155"/>
       <c r="M99" s="156"/>
     </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E100" s="155"/>
       <c r="F100" s="158"/>
       <c r="G100" s="158"/>
@@ -4306,7 +4305,7 @@
       <c r="L100" s="155"/>
       <c r="M100" s="156"/>
     </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E101" s="155"/>
       <c r="F101" s="158"/>
       <c r="G101" s="158"/>
@@ -4317,7 +4316,7 @@
       <c r="L101" s="155"/>
       <c r="M101" s="156"/>
     </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E102" s="155"/>
       <c r="F102" s="158"/>
       <c r="G102" s="158"/>
@@ -4328,50 +4327,50 @@
       <c r="L102" s="166"/>
       <c r="M102" s="167"/>
     </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="173" t="s">
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="174"/>
-      <c r="G103" s="174"/>
-      <c r="H103" s="174"/>
-      <c r="I103" s="174"/>
-      <c r="J103" s="175">
+      <c r="F103" s="196"/>
+      <c r="G103" s="196"/>
+      <c r="H103" s="196"/>
+      <c r="I103" s="196"/>
+      <c r="J103" s="197">
         <f>SUM(J93:J102)</f>
-        <v>36385.604272000004</v>
-      </c>
-      <c r="K103" s="176"/>
+        <v>37356.183419986621</v>
+      </c>
+      <c r="K103" s="187"/>
       <c r="L103" s="168"/>
       <c r="M103" s="169"/>
     </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="177" t="s">
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="178"/>
-      <c r="G108" s="178"/>
-      <c r="H108" s="178"/>
-      <c r="I108" s="178"/>
-      <c r="J108" s="178"/>
-      <c r="K108" s="176"/>
+      <c r="F108" s="186"/>
+      <c r="G108" s="186"/>
+      <c r="H108" s="186"/>
+      <c r="I108" s="186"/>
+      <c r="J108" s="186"/>
+      <c r="K108" s="187"/>
       <c r="L108" s="153"/>
       <c r="M108" s="154"/>
     </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="179" t="s">
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="188" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="178"/>
-      <c r="G109" s="178"/>
-      <c r="H109" s="178"/>
-      <c r="I109" s="178"/>
-      <c r="J109" s="178"/>
-      <c r="K109" s="176"/>
+      <c r="F109" s="186"/>
+      <c r="G109" s="186"/>
+      <c r="H109" s="186"/>
+      <c r="I109" s="186"/>
+      <c r="J109" s="186"/>
+      <c r="K109" s="187"/>
       <c r="L109" s="155"/>
       <c r="M109" s="156"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E110" s="153"/>
       <c r="F110" s="157"/>
       <c r="G110" s="157"/>
@@ -4385,7 +4384,7 @@
       <c r="L110" s="155"/>
       <c r="M110" s="156"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E111" s="155" t="s">
         <v>115</v>
       </c>
@@ -4398,7 +4397,7 @@
       <c r="L111" s="155"/>
       <c r="M111" s="156"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E112" s="159"/>
       <c r="F112" s="160"/>
       <c r="G112" s="160"/>
@@ -4409,20 +4408,20 @@
       <c r="L112" s="155"/>
       <c r="M112" s="156"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="180" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="F113" s="181"/>
-      <c r="G113" s="181"/>
-      <c r="H113" s="181"/>
-      <c r="I113" s="181"/>
-      <c r="J113" s="181"/>
-      <c r="K113" s="182"/>
+      <c r="F113" s="190"/>
+      <c r="G113" s="190"/>
+      <c r="H113" s="190"/>
+      <c r="I113" s="190"/>
+      <c r="J113" s="190"/>
+      <c r="K113" s="191"/>
       <c r="L113" s="155"/>
       <c r="M113" s="156"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E114" s="155"/>
       <c r="F114" s="158"/>
       <c r="G114" s="158"/>
@@ -4433,7 +4432,7 @@
       <c r="L114" s="155"/>
       <c r="M114" s="156"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E115" s="155" t="s">
         <v>116</v>
       </c>
@@ -4450,12 +4449,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="156"/>
-      <c r="L115" s="183" t="s">
+      <c r="L115" s="192" t="s">
         <v>118</v>
       </c>
-      <c r="M115" s="184"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="193"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="155" t="s">
         <v>119</v>
       </c>
@@ -4470,7 +4469,7 @@
       <c r="L116" s="155"/>
       <c r="M116" s="156"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E117" s="155"/>
       <c r="F117" s="158"/>
       <c r="G117" s="158"/>
@@ -4478,10 +4477,10 @@
       <c r="I117" s="158"/>
       <c r="J117" s="158"/>
       <c r="K117" s="156"/>
-      <c r="L117" s="185"/>
-      <c r="M117" s="184"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="194"/>
+      <c r="M117" s="193"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="155" t="s">
         <v>49</v>
       </c>
@@ -4491,13 +4490,13 @@
       <c r="I118" s="158"/>
       <c r="J118" s="164">
         <f>J5</f>
-        <v>40207.664820000005</v>
+        <v>40119.446940000002</v>
       </c>
       <c r="K118" s="156"/>
       <c r="L118" s="155"/>
       <c r="M118" s="156"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E119" s="165" t="s">
         <v>120</v>
       </c>
@@ -4507,13 +4506,13 @@
       <c r="I119" s="158"/>
       <c r="J119" s="164">
         <f>K5</f>
-        <v>0</v>
+        <v>1411.9577257525084</v>
       </c>
       <c r="K119" s="156"/>
       <c r="L119" s="155"/>
       <c r="M119" s="156"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E120" s="165" t="s">
         <v>124</v>
       </c>
@@ -4529,7 +4528,7 @@
       <c r="L120" s="155"/>
       <c r="M120" s="156"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E121" s="165"/>
       <c r="F121" s="158"/>
       <c r="G121" s="158"/>
@@ -4540,7 +4539,7 @@
       <c r="L121" s="155"/>
       <c r="M121" s="156"/>
     </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E122" s="165"/>
       <c r="F122" s="158"/>
       <c r="G122" s="158"/>
@@ -4551,7 +4550,7 @@
       <c r="L122" s="155"/>
       <c r="M122" s="156"/>
     </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F123" s="158"/>
       <c r="G123" s="158"/>
       <c r="H123" s="158"/>
@@ -4561,7 +4560,7 @@
       <c r="L123" s="155"/>
       <c r="M123" s="156"/>
     </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E124" s="165"/>
       <c r="F124" s="158"/>
       <c r="G124" s="158"/>
@@ -4572,7 +4571,7 @@
       <c r="L124" s="155"/>
       <c r="M124" s="156"/>
     </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E125" s="155"/>
       <c r="F125" s="158"/>
       <c r="G125" s="158"/>
@@ -4583,7 +4582,7 @@
       <c r="L125" s="155"/>
       <c r="M125" s="156"/>
     </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E126" s="155"/>
       <c r="F126" s="158"/>
       <c r="G126" s="158"/>
@@ -4594,7 +4593,7 @@
       <c r="L126" s="155"/>
       <c r="M126" s="156"/>
     </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E127" s="155"/>
       <c r="F127" s="158"/>
       <c r="G127" s="158"/>
@@ -4605,24 +4604,57 @@
       <c r="L127" s="166"/>
       <c r="M127" s="167"/>
     </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="173" t="s">
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="195" t="s">
         <v>121</v>
       </c>
-      <c r="F128" s="174"/>
-      <c r="G128" s="174"/>
-      <c r="H128" s="174"/>
-      <c r="I128" s="174"/>
-      <c r="J128" s="175">
+      <c r="F128" s="196"/>
+      <c r="G128" s="196"/>
+      <c r="H128" s="196"/>
+      <c r="I128" s="196"/>
+      <c r="J128" s="197">
         <f>SUM(J118:J127)</f>
-        <v>40155.324820000009</v>
-      </c>
-      <c r="K128" s="176"/>
+        <v>41479.064665752507</v>
+      </c>
+      <c r="K128" s="187"/>
       <c r="L128" s="168"/>
       <c r="M128" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="A6:B6"/>
@@ -4635,39 +4667,6 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4678,16 +4677,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="112" t="s">
         <v>81</v>
       </c>
@@ -4702,17 +4701,17 @@
         <v>83</v>
       </c>
       <c r="H1" s="144">
-        <v>0</v>
+        <v>10296.959999999999</v>
       </c>
       <c r="K1" s="115"/>
       <c r="L1" s="116"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H2" s="117"/>
       <c r="I2" s="117"/>
       <c r="J2" s="117"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="118" t="s">
         <v>84</v>
       </c>
@@ -4739,7 +4738,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="120"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="118"/>
       <c r="C4" s="112" t="s">
         <v>90</v>
@@ -4751,12 +4750,12 @@
       <c r="F4" s="112"/>
       <c r="H4" s="121">
         <f>H1</f>
-        <v>0</v>
+        <v>10296.959999999999</v>
       </c>
       <c r="I4" s="121"/>
       <c r="J4" s="121"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -4781,7 +4780,7 @@
       <c r="G5" s="5"/>
       <c r="H5" s="122">
         <f>H4*(F5/100)</f>
-        <v>0</v>
+        <v>1411.9577257525084</v>
       </c>
       <c r="I5" s="118"/>
       <c r="J5" s="5"/>
@@ -4789,7 +4788,7 @@
       <c r="L5" s="123"/>
       <c r="M5" s="124"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>93</v>
       </c>
@@ -4814,7 +4813,7 @@
       <c r="G6" s="5"/>
       <c r="H6" s="122">
         <f>H4*(F6/100)</f>
-        <v>0</v>
+        <v>1687.4616722408025</v>
       </c>
       <c r="I6" s="118"/>
       <c r="J6" s="5"/>
@@ -4822,7 +4821,7 @@
       <c r="L6" s="123"/>
       <c r="M6" s="124"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>94</v>
       </c>
@@ -4846,7 +4845,7 @@
       </c>
       <c r="H7" s="125">
         <f>H4*(F7/100)</f>
-        <v>0</v>
+        <v>1670.2426755852841</v>
       </c>
       <c r="I7" s="112"/>
       <c r="J7" s="5"/>
@@ -4854,7 +4853,7 @@
       <c r="L7" s="123"/>
       <c r="M7" s="124"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>95</v>
       </c>
@@ -4879,7 +4878,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="122">
         <f>H4*(F8/100)</f>
-        <v>0</v>
+        <v>1842.432642140468</v>
       </c>
       <c r="I8" s="118"/>
       <c r="J8" s="5"/>
@@ -4887,7 +4886,7 @@
       <c r="L8" s="123"/>
       <c r="M8" s="124"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>96</v>
       </c>
@@ -4912,7 +4911,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="122">
         <f>H4*(F9/100)</f>
-        <v>0</v>
+        <v>1033.1397993311036</v>
       </c>
       <c r="I9" s="118"/>
       <c r="J9" s="5"/>
@@ -4920,7 +4919,7 @@
       <c r="L9" s="123"/>
       <c r="M9" s="124"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>97</v>
       </c>
@@ -4945,7 +4944,7 @@
       <c r="G10" s="5"/>
       <c r="H10" s="122">
         <f>H4*(F10/100)</f>
-        <v>0</v>
+        <v>1050.358795986622</v>
       </c>
       <c r="I10" s="118"/>
       <c r="J10" s="5"/>
@@ -4953,7 +4952,7 @@
       <c r="L10" s="123"/>
       <c r="M10" s="124"/>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>98</v>
       </c>
@@ -4978,7 +4977,7 @@
       <c r="G11" s="5"/>
       <c r="H11" s="122">
         <f>H4*(F11/100)</f>
-        <v>0</v>
+        <v>1601.3666889632107</v>
       </c>
       <c r="I11" s="118"/>
       <c r="J11" s="5"/>
@@ -4986,7 +4985,7 @@
       <c r="L11" s="123"/>
       <c r="M11" s="124"/>
     </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="126"/>
       <c r="C12" s="127">
         <f>SUM(C5:C11)</f>
@@ -5007,20 +5006,20 @@
       <c r="G12" s="62"/>
       <c r="H12" s="127">
         <f>SUM(H5:H11)</f>
-        <v>0</v>
+        <v>10296.959999999999</v>
       </c>
       <c r="I12" s="126"/>
       <c r="J12" s="126"/>
       <c r="K12" s="126"/>
       <c r="L12" s="129"/>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="130"/>
       <c r="H13" s="118"/>
       <c r="I13" s="118"/>
       <c r="J13" s="118"/>
     </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>99</v>
       </c>
@@ -5032,7 +5031,7 @@
       <c r="I14" s="118"/>
       <c r="J14" s="118"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>100</v>
       </c>
@@ -5040,7 +5039,7 @@
       <c r="I15" s="118"/>
       <c r="J15" s="118"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="118"/>
       <c r="C16" s="112"/>
       <c r="D16" s="112"/>
@@ -5051,7 +5050,7 @@
       <c r="J16" s="112"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="118"/>
       <c r="C17" s="112"/>
       <c r="D17" s="112"/>
@@ -5061,12 +5060,12 @@
       <c r="I17" s="121"/>
       <c r="J17" s="121"/>
     </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H18" s="118"/>
       <c r="I18" s="118"/>
       <c r="J18" s="118"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C19" s="132"/>
       <c r="D19" s="133"/>
       <c r="E19" s="133"/>
@@ -5079,7 +5078,7 @@
       <c r="L19" s="133"/>
       <c r="M19" s="135"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C20" s="136"/>
       <c r="E20" t="s">
         <v>101</v>
@@ -5095,7 +5094,7 @@
       </c>
       <c r="M20" s="138"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C21" s="136"/>
       <c r="D21" t="s">
         <v>103</v>
@@ -5117,7 +5116,7 @@
       </c>
       <c r="M21" s="138"/>
     </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="139"/>
       <c r="D22" s="140"/>
       <c r="E22" s="140"/>
@@ -5130,16 +5129,16 @@
       <c r="L22" s="140"/>
       <c r="M22" s="141"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K25" s="142" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G26" s="5"/>
       <c r="K26" s="120"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>107</v>
       </c>
@@ -5150,7 +5149,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>97</v>
@@ -5166,7 +5165,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>109</v>
       </c>
@@ -5174,7 +5173,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>110</v>
       </c>
@@ -5182,7 +5181,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J33" s="120" t="s">
         <v>111</v>
       </c>
@@ -5190,7 +5189,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
       <c r="K34" s="114">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5205,39 +5204,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D1" s="56">
         <v>50000</v>
       </c>
-      <c r="H1" s="204">
+      <c r="H1" s="202">
         <v>250000</v>
       </c>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="53" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>57</v>
       </c>
@@ -5260,7 +5259,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5292,18 +5291,18 @@
         <v>54</v>
       </c>
       <c r="K4" s="68"/>
-      <c r="L4" s="202" t="s">
+      <c r="L4" s="200" t="s">
         <v>61</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="200" t="s">
+      <c r="N4" s="198" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5327,14 +5326,14 @@
         <v>60</v>
       </c>
       <c r="K5" s="58"/>
-      <c r="L5" s="203"/>
+      <c r="L5" s="201"/>
       <c r="M5" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="201"/>
+      <c r="N5" s="199"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5382,7 +5381,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5430,7 +5429,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5478,7 +5477,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5526,7 +5525,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5574,7 +5573,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5622,7 +5621,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5670,7 +5669,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5718,7 +5717,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
